--- a/docs/evidence/direction-report-redesign/synthetic-report.xlsx
+++ b/docs/evidence/direction-report-redesign/synthetic-report.xlsx
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Gastos activos · base presupuestal del intervalo</t>
+          <t>Gastos activos · base fiscal canónica documental del intervalo</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Gastos activos · base presupuestal del intervalo</t>
+          <t>Gastos activos · base fiscal canónica documental del intervalo</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">

--- a/docs/evidence/direction-report-redesign/synthetic-report.xlsx
+++ b/docs/evidence/direction-report-redesign/synthetic-report.xlsx
@@ -663,7 +663,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Identificador de cifras: 72f4cad86748b8fa18fb64cf11e1128c3bf1af880a22b27e5accfcfb309f7e3f</t>
+          <t>Identificador de cifras: 10d1ca3061d610cb5ea6e3194f0cb23d681c857aed05be87defd757bcfead315</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -1123,7 +1123,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Lecturas secuenciales con cortes individuales. Proyección mecánica, sin causalidad acreditada. Pagado documental no equivale a salida de caja.</t>
+          <t>Lecturas independientes con cortes individuales. Proyección mecánica, sin causalidad acreditada. Pagado documental no equivale a salida de caja.</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>

--- a/docs/evidence/direction-report-redesign/synthetic-report.xlsx
+++ b/docs/evidence/direction-report-redesign/synthetic-report.xlsx
@@ -663,7 +663,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Identificador de cifras: 10d1ca3061d610cb5ea6e3194f0cb23d681c857aed05be87defd757bcfead315</t>
+          <t>Identificador de cifras: 4c61c4a8b5f1ca95411504cc55085a8ea42f3ca5227923bf12218771fcf3e480</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr"/>
     </row>
-    <row r="12" ht="55" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Comprometido documental</t>
@@ -811,12 +811,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Importe pagable de solicitudes creadas en el intervalo; incluye pagadas/cerradas y reembolsos. No se suma al ejercido.</t>
+          <t>Importe pagable de solicitudes creadas en el intervalo, con su estado actual; incluye enviadas, liquidadas y reembolsos. No equivale a deuda pendiente ni se suma al ejercido.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="55" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Pagado documental</t>
@@ -837,7 +837,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Importe pagable con estado/registro de pago, de solicitudes creadas en el intervalo; no es flujo por fecha efectiva ni caja.</t>
+          <t>Importe pagable de solicitudes creadas en el intervalo, con su estado/registro actual de pago; no acredita por sí solo una transferencia ni es flujo por fecha efectiva o caja.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Torneo sintético Norte</t>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Importe pagable de solicitudes creadas en el intervalo; incluye pagadas/cerradas y reembolsos. No se suma al ejercido.</t>
+          <t>Importe pagable de solicitudes creadas en el intervalo, con su estado actual; incluye enviadas, liquidadas y reembolsos. No equivale a deuda pendiente ni se suma al ejercido.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Torneo sintético Norte</t>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Importe pagable con estado/registro de pago, de solicitudes creadas en el intervalo; no es flujo por fecha efectiva ni caja.</t>
+          <t>Importe pagable de solicitudes creadas en el intervalo, con su estado/registro actual de pago; no acredita por sí solo una transferencia ni es flujo por fecha efectiva o caja.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1">
+    <row r="14" ht="100" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Torneo sintético Sur</t>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Importe pagable de solicitudes creadas en el intervalo; incluye pagadas/cerradas y reembolsos. No se suma al ejercido.</t>
+          <t>Importe pagable de solicitudes creadas en el intervalo, con su estado actual; incluye enviadas, liquidadas y reembolsos. No equivale a deuda pendiente ni se suma al ejercido.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="100" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Torneo sintético Sur</t>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Importe pagable con estado/registro de pago, de solicitudes creadas en el intervalo; no es flujo por fecha efectiva ni caja.</t>
+          <t>Importe pagable de solicitudes creadas en el intervalo, con su estado/registro actual de pago; no acredita por sí solo una transferencia ni es flujo por fecha efectiva o caja.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
